--- a/1. Reporting_Data/IB_Daily Ticker/processed/2025/202511/Ticker_20251107.xlsx
+++ b/1. Reporting_Data/IB_Daily Ticker/processed/2025/202511/Ticker_20251107.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="350">
   <si>
     <t>Symbol</t>
   </si>
@@ -202,6 +202,9 @@
     <t>EFA</t>
   </si>
   <si>
+    <t>EMLC</t>
+  </si>
+  <si>
     <t>EMR</t>
   </si>
   <si>
@@ -403,6 +406,9 @@
     <t>S68</t>
   </si>
   <si>
+    <t>SGOV</t>
+  </si>
+  <si>
     <t>SHOP</t>
   </si>
   <si>
@@ -748,6 +754,9 @@
     <t>EFA US Equity</t>
   </si>
   <si>
+    <t>EMLC US Equity</t>
+  </si>
+  <si>
     <t>EMR US Equity</t>
   </si>
   <si>
@@ -935,6 +944,9 @@
   </si>
   <si>
     <t>S68 SP Equity</t>
+  </si>
+  <si>
+    <t>SGOV US Equity</t>
   </si>
   <si>
     <t>SHOP US Equity</t>
@@ -1409,7 +1421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F163"/>
+  <dimension ref="A1:F165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1437,19 +1449,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -1457,19 +1469,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1477,19 +1489,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1497,19 +1509,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F5" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1517,19 +1529,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E6" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1537,19 +1549,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1557,19 +1569,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F8" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1577,19 +1589,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1597,19 +1609,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E10" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1617,19 +1629,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1637,19 +1649,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D12" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1657,19 +1669,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E13" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F13" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1677,19 +1689,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1697,19 +1709,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1717,19 +1729,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D16" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E16" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1737,19 +1749,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C17" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D17" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E17" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F17" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1757,19 +1769,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E18" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F18" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1777,19 +1789,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E19" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F19" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1797,19 +1809,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D20" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E20" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F20" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1817,19 +1829,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E21" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F21" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1837,19 +1849,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D22" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E22" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F22" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1857,19 +1869,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D23" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E23" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1877,19 +1889,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D24" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E24" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F24" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1897,19 +1909,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D25" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E25" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F25" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1917,19 +1929,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D26" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E26" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F26" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1937,19 +1949,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E27" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F27" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -1957,19 +1969,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E28" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F28" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -1977,19 +1989,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D29" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E29" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F29" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1997,19 +2009,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D30" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E30" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F30" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2017,19 +2029,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E31" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F31" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2037,19 +2049,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E32" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F32" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2057,19 +2069,19 @@
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F33" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2077,19 +2089,19 @@
         <v>38</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E34" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F34" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2097,19 +2109,19 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D35" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E35" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F35" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2117,19 +2129,19 @@
         <v>40</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D36" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E36" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F36" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2137,19 +2149,19 @@
         <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E37" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F37" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2157,19 +2169,19 @@
         <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E38" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F38" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2177,19 +2189,19 @@
         <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D39" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2197,19 +2209,19 @@
         <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D40" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F40" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2217,19 +2229,19 @@
         <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E41" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F41" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2237,19 +2249,19 @@
         <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D42" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E42" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F42" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2257,19 +2269,19 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D43" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E43" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F43" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2277,19 +2289,19 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D44" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E44" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F44" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2297,19 +2309,19 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D45" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E45" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F45" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2317,19 +2329,19 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D46" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E46" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F46" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2337,19 +2349,19 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D47" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F47" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2357,19 +2369,19 @@
         <v>52</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D48" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F48" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2377,19 +2389,19 @@
         <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D49" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F49" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2397,19 +2409,19 @@
         <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D50" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E50" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2417,19 +2429,19 @@
         <v>55</v>
       </c>
       <c r="B51" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D51" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E51" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F51" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2437,19 +2449,19 @@
         <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D52" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E52" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F52" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2457,19 +2469,19 @@
         <v>57</v>
       </c>
       <c r="B53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D53" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2477,19 +2489,19 @@
         <v>58</v>
       </c>
       <c r="B54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D54" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E54" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2497,19 +2509,19 @@
         <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D55" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E55" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F55" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2517,19 +2529,19 @@
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C56" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D56" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E56" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F56" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2537,19 +2549,19 @@
         <v>61</v>
       </c>
       <c r="B57" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D57" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E57" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F57" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2557,19 +2569,19 @@
         <v>62</v>
       </c>
       <c r="B58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C58" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E58" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F58" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2577,19 +2589,19 @@
         <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E59" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F59" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2597,19 +2609,19 @@
         <v>64</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E60" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F60" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2617,19 +2629,19 @@
         <v>65</v>
       </c>
       <c r="B61" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C61" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D61" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E61" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F61" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2637,19 +2649,19 @@
         <v>66</v>
       </c>
       <c r="B62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C62" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D62" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E62" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F62" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2657,19 +2669,19 @@
         <v>67</v>
       </c>
       <c r="B63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D63" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E63" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F63" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2677,19 +2689,19 @@
         <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F64" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2697,19 +2709,19 @@
         <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D65" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F65" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2717,19 +2729,19 @@
         <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C66" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D66" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E66" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F66" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -2737,19 +2749,19 @@
         <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D67" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E67" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F67" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -2757,19 +2769,19 @@
         <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C68" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D68" t="s">
         <v>177</v>
       </c>
       <c r="E68" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F68" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -2777,19 +2789,19 @@
         <v>73</v>
       </c>
       <c r="B69" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D69" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E69" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F69" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -2797,19 +2809,19 @@
         <v>74</v>
       </c>
       <c r="B70" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D70" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E70" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F70" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -2817,19 +2829,19 @@
         <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C71" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D71" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E71" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F71" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -2837,19 +2849,19 @@
         <v>76</v>
       </c>
       <c r="B72" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C72" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D72" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E72" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F72" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -2857,19 +2869,19 @@
         <v>77</v>
       </c>
       <c r="B73" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D73" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E73" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F73" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -2877,19 +2889,19 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C74" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D74" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E74" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F74" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -2897,19 +2909,19 @@
         <v>79</v>
       </c>
       <c r="B75" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C75" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D75" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E75" t="s">
         <v>186</v>
       </c>
       <c r="F75" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -2917,19 +2929,19 @@
         <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C76" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D76" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E76" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F76" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -2937,19 +2949,19 @@
         <v>81</v>
       </c>
       <c r="B77" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C77" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="E77" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F77" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -2957,19 +2969,19 @@
         <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C78" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E78" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F78" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -2977,19 +2989,19 @@
         <v>83</v>
       </c>
       <c r="B79" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D79" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E79" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F79" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -2997,19 +3009,19 @@
         <v>84</v>
       </c>
       <c r="B80" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C80" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D80" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E80" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F80" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3017,19 +3029,19 @@
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C81" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D81" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E81" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F81" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3037,19 +3049,19 @@
         <v>86</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C82" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D82" t="s">
         <v>177</v>
       </c>
       <c r="E82" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F82" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3057,19 +3069,19 @@
         <v>87</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C83" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D83" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E83" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F83" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3077,19 +3089,19 @@
         <v>88</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C84" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D84" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E84" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F84" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3097,19 +3109,19 @@
         <v>89</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C85" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D85" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E85" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F85" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3117,19 +3129,19 @@
         <v>90</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C86" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E86" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F86" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3137,19 +3149,19 @@
         <v>91</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C87" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D87" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E87" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F87" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3157,19 +3169,19 @@
         <v>92</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C88" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D88" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E88" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F88" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3177,19 +3189,19 @@
         <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C89" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D89" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E89" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F89" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3197,19 +3209,19 @@
         <v>94</v>
       </c>
       <c r="B90" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C90" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E90" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F90" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3217,19 +3229,19 @@
         <v>95</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C91" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D91" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E91" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F91" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3237,19 +3249,19 @@
         <v>96</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C92" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E92" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F92" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3257,19 +3269,19 @@
         <v>97</v>
       </c>
       <c r="B93" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C93" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D93" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E93" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F93" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3277,19 +3289,19 @@
         <v>98</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C94" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D94" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E94" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F94" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3297,19 +3309,19 @@
         <v>99</v>
       </c>
       <c r="B95" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C95" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D95" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E95" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F95" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3317,19 +3329,19 @@
         <v>100</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C96" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D96" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E96" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F96" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3337,19 +3349,19 @@
         <v>101</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C97" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D97" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E97" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F97" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3357,19 +3369,19 @@
         <v>102</v>
       </c>
       <c r="B98" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C98" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D98" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E98" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F98" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3377,16 +3389,19 @@
         <v>103</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C99" t="s">
         <v>174</v>
       </c>
       <c r="D99" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E99" t="s">
-        <v>185</v>
+        <v>186</v>
+      </c>
+      <c r="F99" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3394,16 +3409,16 @@
         <v>104</v>
       </c>
       <c r="B100" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C100" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D100" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E100" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3411,19 +3426,16 @@
         <v>105</v>
       </c>
       <c r="B101" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C101" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E101" t="s">
-        <v>184</v>
-      </c>
-      <c r="F101" t="s">
-        <v>285</v>
+        <v>187</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3431,19 +3443,19 @@
         <v>106</v>
       </c>
       <c r="B102" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C102" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E102" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F102" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3451,19 +3463,19 @@
         <v>107</v>
       </c>
       <c r="B103" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C103" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D103" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E103" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F103" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3471,19 +3483,19 @@
         <v>108</v>
       </c>
       <c r="B104" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C104" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D104" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E104" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F104" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3491,19 +3503,19 @@
         <v>109</v>
       </c>
       <c r="B105" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C105" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D105" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E105" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F105" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3511,19 +3523,19 @@
         <v>110</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C106" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D106" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E106" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F106" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3531,19 +3543,19 @@
         <v>111</v>
       </c>
       <c r="B107" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C107" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D107" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E107" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F107" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3551,19 +3563,19 @@
         <v>112</v>
       </c>
       <c r="B108" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C108" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D108" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E108" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F108" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3571,19 +3583,19 @@
         <v>113</v>
       </c>
       <c r="B109" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D109" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E109" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F109" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3591,19 +3603,19 @@
         <v>114</v>
       </c>
       <c r="B110" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C110" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D110" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E110" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F110" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3611,19 +3623,19 @@
         <v>115</v>
       </c>
       <c r="B111" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C111" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D111" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E111" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F111" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3631,19 +3643,19 @@
         <v>116</v>
       </c>
       <c r="B112" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C112" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D112" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E112" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F112" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3651,19 +3663,19 @@
         <v>117</v>
       </c>
       <c r="B113" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C113" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D113" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E113" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F113" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -3671,19 +3683,19 @@
         <v>118</v>
       </c>
       <c r="B114" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C114" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D114" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F114" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -3691,19 +3703,19 @@
         <v>119</v>
       </c>
       <c r="B115" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C115" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D115" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E115" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F115" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -3711,19 +3723,19 @@
         <v>120</v>
       </c>
       <c r="B116" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C116" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D116" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E116" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F116" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -3731,19 +3743,19 @@
         <v>121</v>
       </c>
       <c r="B117" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C117" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D117" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E117" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F117" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -3751,19 +3763,19 @@
         <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C118" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D118" t="s">
         <v>178</v>
       </c>
       <c r="E118" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F118" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -3771,19 +3783,19 @@
         <v>123</v>
       </c>
       <c r="B119" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C119" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D119" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E119" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F119" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -3791,19 +3803,19 @@
         <v>124</v>
       </c>
       <c r="B120" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C120" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D120" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E120" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F120" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -3811,16 +3823,19 @@
         <v>125</v>
       </c>
       <c r="B121" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C121" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D121" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E121" t="s">
-        <v>185</v>
+        <v>187</v>
+      </c>
+      <c r="F121" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -3828,16 +3843,16 @@
         <v>126</v>
       </c>
       <c r="B122" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C122" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D122" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E122" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -3845,19 +3860,16 @@
         <v>127</v>
       </c>
       <c r="B123" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C123" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D123" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E123" t="s">
-        <v>184</v>
-      </c>
-      <c r="F123" t="s">
-        <v>305</v>
+        <v>187</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -3865,19 +3877,19 @@
         <v>128</v>
       </c>
       <c r="B124" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C124" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D124" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E124" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F124" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -3885,19 +3897,19 @@
         <v>129</v>
       </c>
       <c r="B125" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C125" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D125" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E125" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F125" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -3905,19 +3917,19 @@
         <v>130</v>
       </c>
       <c r="B126" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C126" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D126" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E126" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F126" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -3925,19 +3937,19 @@
         <v>131</v>
       </c>
       <c r="B127" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C127" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D127" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E127" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F127" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -3945,19 +3957,19 @@
         <v>132</v>
       </c>
       <c r="B128" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C128" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D128" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E128" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="F128" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -3965,19 +3977,19 @@
         <v>133</v>
       </c>
       <c r="B129" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C129" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D129" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E129" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F129" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -3985,19 +3997,19 @@
         <v>134</v>
       </c>
       <c r="B130" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C130" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D130" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E130" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F130" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4005,19 +4017,19 @@
         <v>135</v>
       </c>
       <c r="B131" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C131" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D131" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E131" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F131" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4025,19 +4037,19 @@
         <v>136</v>
       </c>
       <c r="B132" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C132" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D132" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E132" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F132" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4045,19 +4057,19 @@
         <v>137</v>
       </c>
       <c r="B133" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C133" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D133" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E133" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F133" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4065,19 +4077,19 @@
         <v>138</v>
       </c>
       <c r="B134" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C134" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D134" t="s">
         <v>177</v>
       </c>
       <c r="E134" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F134" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4085,19 +4097,19 @@
         <v>139</v>
       </c>
       <c r="B135" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C135" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D135" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="E135" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F135" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4105,19 +4117,19 @@
         <v>140</v>
       </c>
       <c r="B136" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C136" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D136" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E136" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F136" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4125,19 +4137,19 @@
         <v>141</v>
       </c>
       <c r="B137" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C137" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D137" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E137" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F137" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4145,19 +4157,19 @@
         <v>142</v>
       </c>
       <c r="B138" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C138" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D138" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E138" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F138" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4165,19 +4177,19 @@
         <v>143</v>
       </c>
       <c r="B139" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C139" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D139" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E139" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F139" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4185,19 +4197,19 @@
         <v>144</v>
       </c>
       <c r="B140" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C140" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D140" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E140" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F140" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4205,19 +4217,19 @@
         <v>145</v>
       </c>
       <c r="B141" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C141" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D141" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E141" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F141" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4225,19 +4237,19 @@
         <v>146</v>
       </c>
       <c r="B142" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C142" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D142" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="E142" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F142" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4245,19 +4257,19 @@
         <v>147</v>
       </c>
       <c r="B143" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C143" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D143" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E143" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F143" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4265,19 +4277,19 @@
         <v>148</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C144" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D144" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E144" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F144" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4285,19 +4297,19 @@
         <v>149</v>
       </c>
       <c r="B145" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C145" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D145" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E145" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F145" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4305,19 +4317,19 @@
         <v>150</v>
       </c>
       <c r="B146" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C146" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D146" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E146" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F146" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4325,19 +4337,19 @@
         <v>151</v>
       </c>
       <c r="B147" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C147" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D147" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E147" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F147" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4345,19 +4357,19 @@
         <v>152</v>
       </c>
       <c r="B148" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C148" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D148" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E148" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F148" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4365,19 +4377,19 @@
         <v>153</v>
       </c>
       <c r="B149" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C149" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D149" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E149" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F149" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4385,19 +4397,19 @@
         <v>154</v>
       </c>
       <c r="B150" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C150" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D150" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E150" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F150" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4405,19 +4417,19 @@
         <v>155</v>
       </c>
       <c r="B151" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C151" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D151" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="E151" t="s">
         <v>186</v>
       </c>
       <c r="F151" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -4425,19 +4437,19 @@
         <v>156</v>
       </c>
       <c r="B152" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C152" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D152" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E152" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F152" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -4445,19 +4457,19 @@
         <v>157</v>
       </c>
       <c r="B153" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C153" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D153" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E153" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F153" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -4465,19 +4477,19 @@
         <v>158</v>
       </c>
       <c r="B154" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C154" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D154" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E154" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F154" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -4485,19 +4497,19 @@
         <v>159</v>
       </c>
       <c r="B155" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C155" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D155" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E155" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F155" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -4505,19 +4517,19 @@
         <v>160</v>
       </c>
       <c r="B156" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C156" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D156" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E156" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F156" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -4525,19 +4537,19 @@
         <v>161</v>
       </c>
       <c r="B157" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C157" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D157" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E157" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F157" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -4545,19 +4557,19 @@
         <v>162</v>
       </c>
       <c r="B158" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C158" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D158" t="s">
         <v>177</v>
       </c>
       <c r="E158" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F158" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -4565,19 +4577,19 @@
         <v>163</v>
       </c>
       <c r="B159" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C159" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D159" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E159" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F159" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -4585,19 +4597,19 @@
         <v>164</v>
       </c>
       <c r="B160" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C160" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D160" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E160" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F160" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -4605,19 +4617,19 @@
         <v>165</v>
       </c>
       <c r="B161" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C161" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D161" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E161" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F161" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -4625,19 +4637,19 @@
         <v>166</v>
       </c>
       <c r="B162" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C162" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D162" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E162" t="s">
         <v>186</v>
       </c>
       <c r="F162" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -4645,19 +4657,59 @@
         <v>167</v>
       </c>
       <c r="B163" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C163" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D163" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E163" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F163" t="s">
-        <v>345</v>
+        <v>347</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>168</v>
+      </c>
+      <c r="B164" t="s">
+        <v>173</v>
+      </c>
+      <c r="C164" t="s">
+        <v>174</v>
+      </c>
+      <c r="D164" t="s">
+        <v>182</v>
+      </c>
+      <c r="E164" t="s">
+        <v>188</v>
+      </c>
+      <c r="F164" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>169</v>
+      </c>
+      <c r="B165" t="s">
+        <v>173</v>
+      </c>
+      <c r="C165" t="s">
+        <v>174</v>
+      </c>
+      <c r="D165" t="s">
+        <v>178</v>
+      </c>
+      <c r="E165" t="s">
+        <v>186</v>
+      </c>
+      <c r="F165" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>
